--- a/AAII_Financials/Quarterly/UBS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UBS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
   <si>
     <t>UBS</t>
   </si>
@@ -656,272 +656,278 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="28" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="29" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13581000</v>
+      </c>
+      <c r="E8" s="3">
         <v>14172000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12762000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12525000</v>
       </c>
-      <c r="G8" s="3">
-        <v>11945000</v>
-      </c>
       <c r="H8" s="3">
+        <v>11852000</v>
+      </c>
+      <c r="I8" s="3">
         <v>12457000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11359000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12227000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11811000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12632000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10538000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11456000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8915000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8705000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4543000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3355000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2735000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2552000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2539000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2514000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2463000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2446000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2480000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2429000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2483000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2716000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3468000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3910000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4006000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4013000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>17069000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3650000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3590000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3500000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>14477000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3608000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3627000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3471100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3647100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3422400</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1042,53 +1048,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>13581000</v>
+      </c>
+      <c r="E10" s="3">
         <v>14172000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12762000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12525000</v>
       </c>
-      <c r="G10" s="3">
-        <v>11945000</v>
-      </c>
       <c r="H10" s="3">
+        <v>11852000</v>
+      </c>
+      <c r="I10" s="3">
         <v>12457000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11359000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12227000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11811000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12632000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10538000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11456000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8915000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8705000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1164,8 +1173,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1330,8 +1343,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1452,53 +1468,56 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>620000</v>
+        <v>616000</v>
       </c>
       <c r="E14" s="3">
+        <v>720000</v>
+      </c>
+      <c r="F14" s="3">
         <v>5273000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-133000</v>
       </c>
-      <c r="G14" s="3">
-        <v>1021000</v>
-      </c>
       <c r="H14" s="3">
+        <v>927000</v>
+      </c>
+      <c r="I14" s="3">
         <v>898000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4762000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>14000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1346000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>993000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3764000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>317000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-25762000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-667000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1574,130 +1593,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>248300</v>
+        <v>770000</v>
       </c>
       <c r="E15" s="3">
         <v>248300</v>
       </c>
       <c r="F15" s="3">
+        <v>248300</v>
+      </c>
+      <c r="G15" s="3">
         <v>904000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>898000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>861000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>941000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1006000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>903000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>895000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1022000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>950000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>660000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>525000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-544000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-508000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-503000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-506000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-574000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-518000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-509000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-516000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-627000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-553000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-475000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-472000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-455000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-447000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-443000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-439000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-1214000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-313000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-317000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-320000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-1106000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-270000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-265000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-281700</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-274400</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-279600</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,252 +1762,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9712000</v>
+        <v>9371000</v>
       </c>
       <c r="E17" s="3">
+        <v>9612000</v>
+      </c>
+      <c r="F17" s="3">
         <v>5789000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9830000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8731000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9427000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5550000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10283000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8996000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9263000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7525000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11324000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6982000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7876000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2961000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1755000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1077000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>799000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>741000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>808000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>756000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>805000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>923000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1001000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1364000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1653000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2215000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2857000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2992000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2911000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>11162000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2478000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2414000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2091000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>7953000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1858000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2256000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1714800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1847400</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1588500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4460000</v>
+        <v>4210000</v>
       </c>
       <c r="E18" s="3">
+        <v>4560000</v>
+      </c>
+      <c r="F18" s="3">
         <v>6973000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2695000</v>
       </c>
-      <c r="G18" s="3">
-        <v>3214000</v>
-      </c>
       <c r="H18" s="3">
+        <v>3121000</v>
+      </c>
+      <c r="I18" s="3">
         <v>3030000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5809000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1944000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2815000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3369000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3013000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>132000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1933000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>829000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1582000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1600000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1658000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1753000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1798000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1706000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1707000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1641000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1557000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1428000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1119000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1063000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1253000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1053000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1014000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1102000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>5907000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1172000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1176000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1409000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>6524000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1750000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1371000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1756200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1799700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1833900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2025,8 +2057,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2069,208 +2102,214 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>355000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>723000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>957000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>976000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-69000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1159000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>886000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>657000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>429000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1150000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>463000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>945000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-326000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>292000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>745000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>444000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>84000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>532000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>530000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>691000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1173000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-529000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>131000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-6200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-1027200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-925800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4708300</v>
+        <v>4980000</v>
       </c>
       <c r="E21" s="3">
+        <v>4808300</v>
+      </c>
+      <c r="F21" s="3">
         <v>7221300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3599000</v>
       </c>
-      <c r="G21" s="3">
-        <v>4112000</v>
-      </c>
       <c r="H21" s="3">
+        <v>4019000</v>
+      </c>
+      <c r="I21" s="3">
         <v>3891000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6750000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2950000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3718000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4264000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4035000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1082000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2593000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1354000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2481000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2831000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3118000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3235000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2303000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3383000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3103000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2814000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2613000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3131000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2056000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2480000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1422000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1793000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2203000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1989000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>7284000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2029000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2010000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2404000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>6475000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1493000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1768000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2035800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1057300</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1188800</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2313,8 +2352,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2391,252 +2430,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3594000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3840000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1700000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2828000</v>
       </c>
-      <c r="G23" s="3">
-        <v>2193000</v>
-      </c>
       <c r="H23" s="3">
+        <v>2194000</v>
+      </c>
+      <c r="I23" s="3">
         <v>2132000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1047000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1930000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1469000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2376000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-751000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-185000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>27695000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1496000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1937000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2323000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2615000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2729000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1729000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2865000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2593000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2298000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1986000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2578000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1582000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2008000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>927000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1345000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1759000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1546000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5991000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1704000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1706000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2100000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>5351000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1221000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1502000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1750000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>772500</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>908200</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>782000</v>
+      </c>
+      <c r="E24" s="3">
         <v>786000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>495000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>341000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-209000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>430000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>268000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>502000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>293000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>612000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-473000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>526000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>361000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>459000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>280000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>580000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>497000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>585000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>369000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>576000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>581000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>471000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>341000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>485000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>347000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>410000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>200000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>294000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>366000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>407000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1468000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>448000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>322000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>533000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1366000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>272000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>327000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>388300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>113900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>50700</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2757,252 +2805,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2812000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3054000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1205000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2487000</v>
       </c>
-      <c r="G26" s="3">
-        <v>2402000</v>
-      </c>
       <c r="H26" s="3">
+        <v>2403000</v>
+      </c>
+      <c r="I26" s="3">
         <v>1702000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>779000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1428000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1176000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1764000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-278000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-711000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>27334000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1037000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1657000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1743000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2118000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2144000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1360000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2289000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2012000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1827000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1645000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2093000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1235000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1598000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>727000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1051000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1393000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1139000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4523000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1256000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1384000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1567000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3985000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>949000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1175000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1361700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>658600</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>857400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3040000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1199000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2481000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2395000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1692000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>770000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1425000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1136000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1755000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-279000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-715000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>27331000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1029000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1653000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1733000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2108000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2136000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1348000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2279000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2006000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1824000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1636000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2093000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1232000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1595000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>722000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1049000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1392000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1141000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4516000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1253000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1382000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1566000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3908000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>946000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1174000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1314100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>658600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>856400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3123,8 +3180,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3209,8 +3269,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3227,12 +3287,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-2939000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3245,8 +3305,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3367,8 +3430,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3489,8 +3555,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3533,208 +3602,214 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>-355000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-723000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-957000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-976000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>69000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1159000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-886000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-657000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-429000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1150000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-463000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-945000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>326000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-292000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-745000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-444000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-84000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-532000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-530000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-691000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1173000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>529000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-131000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>6200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>1027200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>925800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3040000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1199000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2481000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2395000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1692000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>770000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1425000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1136000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1755000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-279000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-715000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>27331000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1029000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1653000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1733000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2108000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2136000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1348000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2279000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2006000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1824000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1636000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2093000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1232000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1595000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>722000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1049000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1392000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1141000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4516000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1253000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1382000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1566000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>969000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>946000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1174000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1314100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>658600</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>856400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3855,257 +3930,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3040000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1199000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2481000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2395000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1692000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>770000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1425000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1136000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1755000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-279000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-715000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>27331000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1029000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1653000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1733000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2108000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2136000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1348000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2279000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2006000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1824000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1636000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2093000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1232000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1595000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>722000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1049000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1392000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1141000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4516000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1253000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1382000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1566000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>969000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>946000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1174000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1314100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>658600</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>856400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4148,8 +4232,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4192,297 +4277,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>242675000</v>
+      </c>
+      <c r="E41" s="3">
         <v>225456000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>227549000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>239703000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>256014000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>250873000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>240383000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>263292000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>268147000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>291541000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>329273000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>281265000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>283500000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>157538000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>169445000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>166406000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>190353000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>206773000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>192817000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>174478000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>160672000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>158914000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>158231000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>149176000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>149549000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>139258000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>107068000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>91292000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>101457000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>110618000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>108370000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>92632000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>102262000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>92800000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>90045000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>94563000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>100071000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>112800200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>111594900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>98043000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>332696000</v>
+      </c>
+      <c r="E42" s="3">
         <v>302956000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>238225000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>287364000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>292855000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>255009000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>273176000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>272535000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>257740000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>269951000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>261844000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>288779000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>282882000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>194439000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>469088000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>491248000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>458019000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>449521000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>436003000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>439212000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>445009000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>477198000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>494316000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>466549000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>482660000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>533653000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>458522000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>478744000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>464597000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>444183000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>449377000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>444115000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>447151000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>431487000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>516773000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>413928000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>394448000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>409974800</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>443575300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>458292200</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>134839000</v>
+      </c>
+      <c r="E43" s="3">
         <v>148675000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>126063000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>133254000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>146092000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>136976000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>150700000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>124195000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>114881000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>131619000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>127453000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>116968000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>115938000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>84946000</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4558,8 +4650,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4602,8 +4697,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4680,53 +4775,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>55069000</v>
+      </c>
+      <c r="E45" s="3">
         <v>42625000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100710000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>60808000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>60291000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>60187000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>84618000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>72551000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>55838000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>61721000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>95880000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>60459000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>66197000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>45980000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4802,53 +4900,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>818415000</v>
+      </c>
+      <c r="E46" s="3">
         <v>770336000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>739655000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>766469000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>802616000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>743906000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>797961000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>781669000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>742132000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>803594000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>870527000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>805812000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>805969000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>516894000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4924,374 +5025,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>170099000</v>
+      </c>
+      <c r="E47" s="3">
         <v>200115000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>166142000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>162218000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>165295000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>152136000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>132946000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>173841000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>167658000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>146401000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>150743000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>167166000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>155398000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>107159000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1101000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1032000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1094000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1150000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1243000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1188000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1198000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1542000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1557000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1483000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1054000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1042000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1051000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1009000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1049000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1095000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1099000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>982000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1026000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1037000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1045000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>987000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>972000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1011700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>997200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>980600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15989000</v>
+      </c>
+      <c r="E48" s="3">
         <v>16178000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11199000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>16153000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16376000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15564000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10613000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>16571000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16440000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16770000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12435000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17919000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18325000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12249000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12288000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11829000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12049000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12491000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12888000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12827000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12895000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12716000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13109000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12911000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12875000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12764000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12804000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12487000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12694000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12612000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9348000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9042000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9083000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8860000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>9057000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8647000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>8424000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>8665200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>8626900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>8401200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6846000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6900000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11806000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6982000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7023000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6909000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11772000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7048000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7313000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7384000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12929000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7462000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7569000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6272000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6267000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6210000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6312000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6383000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6378000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6401000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6452000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6427000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6480000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6428000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6414000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6407000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6469000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>6560000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6624000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6621000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>6647000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>6316000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>6391000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>6235000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>6563000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>6388000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>6226000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>6687400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>6788900</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>6570400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5412,8 +5525,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5534,130 +5650,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1991000</v>
+      </c>
+      <c r="E52" s="3">
         <v>21015000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3905000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2339000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2191000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2254000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4414000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2695000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2823000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2633000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4526000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2398000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2695000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1226000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9758000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9620000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10282000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10462000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8908000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8896000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9056000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9443000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9458000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9419000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9547000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9518000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9747000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9567000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9669000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9886000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10187000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9719000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9924000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9796000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>10154000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>12762000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>12467000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>18735700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>19056700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>18972800</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5778,130 +5900,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1707284000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1686521000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1617427000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1632251000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1669991000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1543363000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1565028000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1623941000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1560976000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1607120000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1716924000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1644522000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1678780000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1053134000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1104364000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1111753000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1113193000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1139922000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1117182000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1088773000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1086519000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1107712000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1125765000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1065153000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1063849000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1098099000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>972194000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>973118000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>968728000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>956579000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>958489000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>932471000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>944482000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>919361000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>939279000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>913599000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>890831000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>941917300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>968227800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>968424500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5944,8 +6072,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5988,175 +6117,179 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>784845000</v>
+      </c>
+      <c r="E57" s="3">
         <v>785698000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>788367000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>783115000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800045000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>744866000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>745777000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>775994000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>756830000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>763959000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>792029000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>733071000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>712546000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>505581000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>51236000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>53775000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>56949000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>55947000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>50672000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>51652000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>46116000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>53183000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>46418000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>45978000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>53422000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>51584000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>46573000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>45117000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>45130000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>45872000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>48716000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>49084000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>48034000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>43960000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>48644000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>32407000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>31230000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>34033400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>34716800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>36101300</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>295420000</v>
+      </c>
+      <c r="E58" s="3">
         <v>299381000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>307750000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>244665000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>272054000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>219576000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>327414000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>263363000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>233334000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>261466000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>345053000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>331736000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>368428000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>176697000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6232,175 +6365,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100626000</v>
+      </c>
+      <c r="E59" s="3">
         <v>96761000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>89074000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>88646000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>86413000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>76437000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>73607000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>72670000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>67639000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>74498000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>77201000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>78097000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>83410000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>67580000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9180000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8837000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8268000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7221000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9850000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9098000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8248000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7293000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9326000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9319000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8071000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7000000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9477000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7710000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7127000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6437000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9126000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9750000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>9266000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>8498000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4610000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2845000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2799000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3395500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>3055800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2493500</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1276541000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1257007000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1263828000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1195849000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1233295000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1115781000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1212976000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1183435000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1122072000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1162741000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1275129000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1200992000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1223883000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>802324000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6476,252 +6615,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>303793000</v>
+      </c>
+      <c r="E61" s="3">
         <v>274922000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>225757000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>308011000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>307365000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>299960000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>223925000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>310629000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>312585000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>315785000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>311508000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>317660000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>321195000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>169427000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>161917000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>157679000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>165887000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>168845000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>173414000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>170702000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>176014000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>167590000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>157736000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>157487000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>153024000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>145394000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>159412000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>161796000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>167971000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>166959000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>150277000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>152425000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>149051000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>143780000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>141672000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>141440000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>131622000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>140404100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>136784900</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>134172300</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>35814000</v>
+      </c>
+      <c r="E62" s="3">
         <v>62090000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>35494000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>36316000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>37838000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>38342000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40896000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>40499000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>40262000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>41056000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>42376000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>38719000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>44028000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23236000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4544000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4008000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5503000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6037000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6387000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4432000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4563000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4245000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4762000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4086000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4047000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3995000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8055000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5368000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5012000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5120000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5271000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4305000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4655000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4819000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>18646000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>10990000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>10212000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>16257700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>18387700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>10747700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6842,8 +6990,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6964,8 +7115,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7086,130 +7240,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1617854000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1594019000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1526943000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1542047000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1580292000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1455773000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1479455000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1536352000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1476758000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1521354000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1630769000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1559124000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1591145000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>996028000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1047488000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1055996000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1056348000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1081066000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1056520000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1028554000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1027753000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1049686000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1066319000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1005702000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1006847000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1040150000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>917693000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>916930000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>915548000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>902912000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>905562000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>881349000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>893708000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>868118000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>886784000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>860106000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>839087000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>886350200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>912703200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>913231300</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7252,8 +7412,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7374,8 +7535,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7496,8 +7660,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7618,8 +7785,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7740,130 +7910,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>86004000</v>
+      </c>
+      <c r="E72" s="3">
         <v>86478000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>82740000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>81666000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>79726000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>80023000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>78035000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>77197000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>76176000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>76436000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>74397000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>76726000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>78180000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>51140000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>50004000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>48813000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>46598000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>46451000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>43851000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>42330000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>40143000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>40482000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>38776000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>37936000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>35959000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>36796000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>34122000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>35611000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>32548000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>31085000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>30448000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>36497000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>35584000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>33807000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>25932000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>35107000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>34074000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>34031300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>32851900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>32420100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7984,8 +8160,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8106,8 +8285,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8228,130 +8410,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>89165000</v>
+      </c>
+      <c r="E76" s="3">
         <v>92247000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>90213000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>89899000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>89277000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>87185000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>85079000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>87025000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>83683000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>85260000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>85624000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>84856000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>86999000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>56754000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>56876000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>55757000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>56845000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>58856000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>60662000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>60219000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>58766000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>58026000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>59446000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>59451000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>57002000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>57949000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>54501000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>56188000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>53180000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>53667000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>52927000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>51122000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>50774000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>51243000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>52495000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>53493000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>51744000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>55567000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>55524600</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>55193200</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8472,257 +8660,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3040000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1199000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2481000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2395000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1692000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>770000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1425000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1136000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1755000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-279000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-715000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>27331000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1029000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1653000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1733000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2108000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2136000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1348000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2279000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2006000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1824000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1636000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2093000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1232000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1595000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>722000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1049000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1392000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1141000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4516000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1253000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1382000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1566000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>969000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>946000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1174000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1314100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>658600</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>856400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8765,130 +8962,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>898000</v>
+      </c>
+      <c r="E83" s="3">
         <v>861000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>751000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1006000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>903000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>895000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>888000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>950000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>660000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>525000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>515000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>508000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>503000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>506000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>544000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>508000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>503000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>506000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>574000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>518000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>510000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>516000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>627000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>553000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>474000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>472000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>495000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>448000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>444000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>443000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1293000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>325000</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>304000</v>
       </c>
       <c r="AJ83" s="3">
         <v>304000</v>
       </c>
       <c r="AK83" s="3">
+        <v>304000</v>
+      </c>
+      <c r="AL83" s="3">
         <v>1124000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>272000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>266000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>285800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>284800</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>280600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9009,8 +9210,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9131,8 +9335,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9253,8 +9460,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9375,8 +9585,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9497,130 +9710,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
         <v>1025000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10924000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6012000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>28853000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12830000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9423000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7669000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14089000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5852000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1654000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>31964000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2880000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-353000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3150000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9129000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>27279000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10133000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>23428000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2498000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>362000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3450000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-7273000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4949000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>35832000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>22504000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4448000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2346000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3995000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>28913000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-9095000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>13182000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3300000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-50911000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-14899000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-13982000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-9035900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>19147800</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>3681300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9663,130 +9882,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3">
         <v>-664000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-589000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-551000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-558000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-538000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-557000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-413000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-458000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-397000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-455000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-375000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-462000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-420000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-359000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-402000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-487000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-458000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-464000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-432000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-525000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-498000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-457000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-374000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-430000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-372000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-415000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-367000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1688000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-454000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-365000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1593000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-418000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-405000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-326200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-407000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-447300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9907,8 +10130,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10029,130 +10255,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3">
         <v>-4435000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4217000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6987000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7163000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1098000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-742000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1234000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1315000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>216000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1857000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>107161000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2396000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4004000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3813000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1128000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3502000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1497000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-917000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>688000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-393000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>490000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>542000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6321000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1496000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>411000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1346000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-491000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-132000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6132000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>251000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1571000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>5186000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>697000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>1197000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-222600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-3961900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>2065900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10195,52 +10427,53 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>2866000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>2256000</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>1679000</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10264,11 +10497,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1299000</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -10288,11 +10521,11 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-2440000</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
@@ -10300,11 +10533,11 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-2229000</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
         <v>0</v>
       </c>
@@ -10317,8 +10550,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10439,8 +10675,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10561,8 +10800,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10683,252 +10925,261 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
         <v>-4610000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-24471000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1713000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-16434000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3944000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-23477000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-28453000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-43363000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>26391000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4608000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13121000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-23354000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-155000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5109000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>289000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4119000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>6677000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-7127000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1859000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>12654000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-161000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>225000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>8612000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3756000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-11369000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1944000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-12417000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>116000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>190000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-830000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-472000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>4884000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>26988000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>9428000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>5097000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>12460400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-4483800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-2197400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>15948000</v>
+      </c>
+      <c r="E101" s="3">
         <v>5044000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-13448000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>11241000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-881000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-12852000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>15452000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4457000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2213000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>747000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>10129000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6132000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6925000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2731000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>10129000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-6132000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-6925000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2731000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1589000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1506000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2593000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-7983000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5458000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>4031000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1739000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-176000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2753000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2105000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1902000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1289000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1726000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1073000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1975000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>2110000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>5745000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1178000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-1447000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-57000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>747600</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-243300</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10936,117 +11187,120 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-8329000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-19349000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4662000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10300000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-31320000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3555000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20431000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-40811000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>47911000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3360000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>128217000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-27883000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5617000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-18204000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16893000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>16927000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>16902000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13878000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1076000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4640000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>9237000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2475000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>8979000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>37916000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>14299000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-9843000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-13352000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2690000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>21245000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-10474000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>8385000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>8642000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-14180000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-3596000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-9135000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>3144900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>11449700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>3306400</v>
       </c>
     </row>
